--- a/order_database.xlsx
+++ b/order_database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b5bd79253e10ed0a/바탕 화면/스트라우만/주문시스템/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{5DB33D50-9574-433D-B31B-28221E15E2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A682A7A-B796-4192-B749-442195C0C71E}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="8_{5DB33D50-9574-433D-B31B-28221E15E2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33FE9D1E-A686-4155-87E6-62D4BB22B8B5}"/>
   <bookViews>
-    <workbookView xWindow="795" yWindow="2775" windowWidth="21600" windowHeight="11295" xr2:uid="{EEF6FA6F-BCB9-4450-983B-E3F7A95A94F4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EEF6FA6F-BCB9-4450-983B-E3F7A95A94F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="248">
   <si>
     <t>제품군 대그룹 (Product Group)</t>
   </si>
@@ -774,6 +774,14 @@
   </si>
   <si>
     <t>BLX-WB</t>
+  </si>
+  <si>
+    <t>Roxolid SLA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Roxolid SLActive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -838,6 +846,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4198,7 +4210,7 @@
         <v>110</v>
       </c>
       <c r="B179" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C179">
         <v>3.75</v>
@@ -4215,7 +4227,7 @@
         <v>110</v>
       </c>
       <c r="B180" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C180">
         <v>3.75</v>
@@ -4232,7 +4244,7 @@
         <v>110</v>
       </c>
       <c r="B181" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C181">
         <v>3.75</v>
@@ -4249,7 +4261,7 @@
         <v>110</v>
       </c>
       <c r="B182" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C182">
         <v>3.75</v>
@@ -4266,7 +4278,7 @@
         <v>110</v>
       </c>
       <c r="B183" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C183">
         <v>3.75</v>
@@ -4283,7 +4295,7 @@
         <v>110</v>
       </c>
       <c r="B184" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C184">
         <v>3.75</v>
@@ -4300,7 +4312,7 @@
         <v>110</v>
       </c>
       <c r="B185" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C185">
         <v>3.75</v>
@@ -4317,7 +4329,7 @@
         <v>110</v>
       </c>
       <c r="B186" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C186">
         <v>3.75</v>
@@ -4334,7 +4346,7 @@
         <v>110</v>
       </c>
       <c r="B187" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C187">
         <v>3.75</v>
@@ -4351,7 +4363,7 @@
         <v>110</v>
       </c>
       <c r="B188" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C188">
         <v>3.75</v>
@@ -4368,7 +4380,7 @@
         <v>110</v>
       </c>
       <c r="B189" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C189">
         <v>3.75</v>
@@ -4385,7 +4397,7 @@
         <v>110</v>
       </c>
       <c r="B190" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C190">
         <v>3.75</v>
@@ -4402,7 +4414,7 @@
         <v>123</v>
       </c>
       <c r="B191" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C191">
         <v>3.75</v>
@@ -4419,7 +4431,7 @@
         <v>123</v>
       </c>
       <c r="B192" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C192">
         <v>3.75</v>
@@ -4436,7 +4448,7 @@
         <v>123</v>
       </c>
       <c r="B193" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C193">
         <v>3.75</v>
@@ -4453,7 +4465,7 @@
         <v>123</v>
       </c>
       <c r="B194" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C194">
         <v>3.75</v>
@@ -4470,7 +4482,7 @@
         <v>123</v>
       </c>
       <c r="B195" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C195">
         <v>3.75</v>
@@ -4487,7 +4499,7 @@
         <v>123</v>
       </c>
       <c r="B196" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C196">
         <v>3.75</v>
@@ -4504,7 +4516,7 @@
         <v>123</v>
       </c>
       <c r="B197" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C197">
         <v>3.75</v>
@@ -4521,7 +4533,7 @@
         <v>123</v>
       </c>
       <c r="B198" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C198">
         <v>3.75</v>
@@ -4538,7 +4550,7 @@
         <v>123</v>
       </c>
       <c r="B199" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C199">
         <v>3.75</v>
@@ -4555,7 +4567,7 @@
         <v>123</v>
       </c>
       <c r="B200" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C200">
         <v>3.75</v>
@@ -4572,7 +4584,7 @@
         <v>123</v>
       </c>
       <c r="B201" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C201">
         <v>3.75</v>
@@ -4589,7 +4601,7 @@
         <v>123</v>
       </c>
       <c r="B202" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C202">
         <v>3.75</v>
@@ -4606,7 +4618,7 @@
         <v>136</v>
       </c>
       <c r="B203" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C203">
         <v>3.75</v>
@@ -4623,7 +4635,7 @@
         <v>136</v>
       </c>
       <c r="B204" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C204">
         <v>3.75</v>
@@ -4640,7 +4652,7 @@
         <v>136</v>
       </c>
       <c r="B205" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C205">
         <v>3.75</v>
@@ -4657,7 +4669,7 @@
         <v>136</v>
       </c>
       <c r="B206" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C206">
         <v>3.75</v>
@@ -4674,7 +4686,7 @@
         <v>136</v>
       </c>
       <c r="B207" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C207">
         <v>3.75</v>
@@ -4691,7 +4703,7 @@
         <v>136</v>
       </c>
       <c r="B208" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C208">
         <v>3.75</v>
@@ -4708,7 +4720,7 @@
         <v>136</v>
       </c>
       <c r="B209" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C209">
         <v>3.75</v>
@@ -4725,7 +4737,7 @@
         <v>136</v>
       </c>
       <c r="B210" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C210">
         <v>3.75</v>
@@ -4742,7 +4754,7 @@
         <v>136</v>
       </c>
       <c r="B211" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C211">
         <v>3.75</v>
@@ -4759,7 +4771,7 @@
         <v>136</v>
       </c>
       <c r="B212" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C212">
         <v>3.75</v>
@@ -4776,7 +4788,7 @@
         <v>136</v>
       </c>
       <c r="B213" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C213">
         <v>3.75</v>
@@ -4793,7 +4805,7 @@
         <v>136</v>
       </c>
       <c r="B214" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C214">
         <v>3.75</v>
@@ -4810,7 +4822,7 @@
         <v>149</v>
       </c>
       <c r="B215" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C215">
         <v>3.75</v>
@@ -4827,7 +4839,7 @@
         <v>149</v>
       </c>
       <c r="B216" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C216">
         <v>3.75</v>
@@ -4844,7 +4856,7 @@
         <v>149</v>
       </c>
       <c r="B217" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C217">
         <v>3.75</v>
@@ -4861,7 +4873,7 @@
         <v>149</v>
       </c>
       <c r="B218" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C218">
         <v>3.75</v>
@@ -4878,7 +4890,7 @@
         <v>149</v>
       </c>
       <c r="B219" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C219">
         <v>3.75</v>
@@ -4895,7 +4907,7 @@
         <v>149</v>
       </c>
       <c r="B220" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C220">
         <v>3.75</v>
@@ -4912,7 +4924,7 @@
         <v>149</v>
       </c>
       <c r="B221" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C221">
         <v>3.75</v>
@@ -4929,7 +4941,7 @@
         <v>149</v>
       </c>
       <c r="B222" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C222">
         <v>3.75</v>
@@ -4946,7 +4958,7 @@
         <v>149</v>
       </c>
       <c r="B223" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C223">
         <v>3.75</v>
@@ -4963,7 +4975,7 @@
         <v>149</v>
       </c>
       <c r="B224" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C224">
         <v>3.75</v>
@@ -4980,7 +4992,7 @@
         <v>149</v>
       </c>
       <c r="B225" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C225">
         <v>3.75</v>
@@ -4997,7 +5009,7 @@
         <v>149</v>
       </c>
       <c r="B226" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C226">
         <v>3.75</v>
@@ -5014,7 +5026,7 @@
         <v>110</v>
       </c>
       <c r="B227" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C227">
         <v>4.5</v>
@@ -5031,7 +5043,7 @@
         <v>110</v>
       </c>
       <c r="B228" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C228">
         <v>4.5</v>
@@ -5048,7 +5060,7 @@
         <v>110</v>
       </c>
       <c r="B229" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C229">
         <v>4.5</v>
@@ -5065,7 +5077,7 @@
         <v>110</v>
       </c>
       <c r="B230" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C230">
         <v>4.5</v>
@@ -5082,7 +5094,7 @@
         <v>110</v>
       </c>
       <c r="B231" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C231">
         <v>4.5</v>
@@ -5099,7 +5111,7 @@
         <v>110</v>
       </c>
       <c r="B232" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C232">
         <v>4.5</v>
@@ -5116,7 +5128,7 @@
         <v>110</v>
       </c>
       <c r="B233" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C233">
         <v>4.5</v>
@@ -5133,7 +5145,7 @@
         <v>110</v>
       </c>
       <c r="B234" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C234">
         <v>4.5</v>
@@ -5150,7 +5162,7 @@
         <v>110</v>
       </c>
       <c r="B235" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C235">
         <v>4.5</v>
@@ -5167,7 +5179,7 @@
         <v>110</v>
       </c>
       <c r="B236" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C236">
         <v>4.5</v>
@@ -5184,7 +5196,7 @@
         <v>110</v>
       </c>
       <c r="B237" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C237">
         <v>4.5</v>
@@ -5201,7 +5213,7 @@
         <v>110</v>
       </c>
       <c r="B238" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C238">
         <v>4.5</v>
@@ -5218,7 +5230,7 @@
         <v>123</v>
       </c>
       <c r="B239" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C239">
         <v>4.5</v>
@@ -5235,7 +5247,7 @@
         <v>123</v>
       </c>
       <c r="B240" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C240">
         <v>4.5</v>
@@ -5252,7 +5264,7 @@
         <v>123</v>
       </c>
       <c r="B241" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C241">
         <v>4.5</v>
@@ -5269,7 +5281,7 @@
         <v>123</v>
       </c>
       <c r="B242" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C242">
         <v>4.5</v>
@@ -5286,7 +5298,7 @@
         <v>123</v>
       </c>
       <c r="B243" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C243">
         <v>4.5</v>
@@ -5303,7 +5315,7 @@
         <v>123</v>
       </c>
       <c r="B244" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C244">
         <v>4.5</v>
@@ -5320,7 +5332,7 @@
         <v>123</v>
       </c>
       <c r="B245" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C245">
         <v>4.5</v>
@@ -5337,7 +5349,7 @@
         <v>123</v>
       </c>
       <c r="B246" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C246">
         <v>4.5</v>
@@ -5354,7 +5366,7 @@
         <v>123</v>
       </c>
       <c r="B247" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C247">
         <v>4.5</v>
@@ -5371,7 +5383,7 @@
         <v>123</v>
       </c>
       <c r="B248" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C248">
         <v>4.5</v>
@@ -5388,7 +5400,7 @@
         <v>123</v>
       </c>
       <c r="B249" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C249">
         <v>4.5</v>
@@ -5405,7 +5417,7 @@
         <v>123</v>
       </c>
       <c r="B250" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C250">
         <v>4.5</v>
@@ -5422,7 +5434,7 @@
         <v>136</v>
       </c>
       <c r="B251" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C251">
         <v>4.5</v>
@@ -5439,7 +5451,7 @@
         <v>136</v>
       </c>
       <c r="B252" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C252">
         <v>4.5</v>
@@ -5456,7 +5468,7 @@
         <v>136</v>
       </c>
       <c r="B253" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C253">
         <v>4.5</v>
@@ -5473,7 +5485,7 @@
         <v>136</v>
       </c>
       <c r="B254" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C254">
         <v>4.5</v>
@@ -5490,7 +5502,7 @@
         <v>136</v>
       </c>
       <c r="B255" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C255">
         <v>4.5</v>
@@ -5507,7 +5519,7 @@
         <v>136</v>
       </c>
       <c r="B256" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C256">
         <v>4.5</v>
@@ -5524,7 +5536,7 @@
         <v>136</v>
       </c>
       <c r="B257" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C257">
         <v>4.5</v>
@@ -5541,7 +5553,7 @@
         <v>136</v>
       </c>
       <c r="B258" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C258">
         <v>4.5</v>
@@ -5558,7 +5570,7 @@
         <v>136</v>
       </c>
       <c r="B259" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C259">
         <v>4.5</v>
@@ -5575,7 +5587,7 @@
         <v>136</v>
       </c>
       <c r="B260" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C260">
         <v>4.5</v>
@@ -5592,7 +5604,7 @@
         <v>136</v>
       </c>
       <c r="B261" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C261">
         <v>4.5</v>
@@ -5609,7 +5621,7 @@
         <v>136</v>
       </c>
       <c r="B262" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C262">
         <v>4.5</v>
@@ -5626,7 +5638,7 @@
         <v>149</v>
       </c>
       <c r="B263" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C263">
         <v>4.5</v>
@@ -5643,7 +5655,7 @@
         <v>149</v>
       </c>
       <c r="B264" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C264">
         <v>4.5</v>
@@ -5660,7 +5672,7 @@
         <v>149</v>
       </c>
       <c r="B265" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C265">
         <v>4.5</v>
@@ -5677,7 +5689,7 @@
         <v>149</v>
       </c>
       <c r="B266" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C266">
         <v>4.5</v>
@@ -5694,7 +5706,7 @@
         <v>149</v>
       </c>
       <c r="B267" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C267">
         <v>4.5</v>
@@ -5711,7 +5723,7 @@
         <v>149</v>
       </c>
       <c r="B268" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C268">
         <v>4.5</v>
@@ -5728,7 +5740,7 @@
         <v>149</v>
       </c>
       <c r="B269" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C269">
         <v>4.5</v>
@@ -5745,7 +5757,7 @@
         <v>149</v>
       </c>
       <c r="B270" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C270">
         <v>4.5</v>
@@ -5762,7 +5774,7 @@
         <v>149</v>
       </c>
       <c r="B271" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C271">
         <v>4.5</v>
@@ -5779,7 +5791,7 @@
         <v>149</v>
       </c>
       <c r="B272" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C272">
         <v>4.5</v>
@@ -5796,7 +5808,7 @@
         <v>149</v>
       </c>
       <c r="B273" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C273">
         <v>4.5</v>
@@ -5813,7 +5825,7 @@
         <v>149</v>
       </c>
       <c r="B274" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C274">
         <v>4.5</v>
@@ -5830,7 +5842,7 @@
         <v>210</v>
       </c>
       <c r="B275" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C275">
         <v>5.5</v>
@@ -5847,7 +5859,7 @@
         <v>210</v>
       </c>
       <c r="B276" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C276">
         <v>5.5</v>
@@ -5864,7 +5876,7 @@
         <v>210</v>
       </c>
       <c r="B277" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C277">
         <v>5.5</v>
@@ -5881,7 +5893,7 @@
         <v>210</v>
       </c>
       <c r="B278" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C278">
         <v>5.5</v>
@@ -5898,7 +5910,7 @@
         <v>210</v>
       </c>
       <c r="B279" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C279">
         <v>5.5</v>
@@ -5915,7 +5927,7 @@
         <v>210</v>
       </c>
       <c r="B280" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C280">
         <v>5.5</v>
@@ -5932,7 +5944,7 @@
         <v>210</v>
       </c>
       <c r="B281" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C281">
         <v>5.5</v>
@@ -5949,7 +5961,7 @@
         <v>210</v>
       </c>
       <c r="B282" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C282">
         <v>5.5</v>
@@ -5966,7 +5978,7 @@
         <v>219</v>
       </c>
       <c r="B283" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C283">
         <v>5.5</v>
@@ -5983,7 +5995,7 @@
         <v>219</v>
       </c>
       <c r="B284" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C284">
         <v>5.5</v>
@@ -6000,7 +6012,7 @@
         <v>219</v>
       </c>
       <c r="B285" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C285">
         <v>5.5</v>
@@ -6017,7 +6029,7 @@
         <v>219</v>
       </c>
       <c r="B286" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C286">
         <v>5.5</v>
@@ -6034,7 +6046,7 @@
         <v>219</v>
       </c>
       <c r="B287" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C287">
         <v>5.5</v>
@@ -6051,7 +6063,7 @@
         <v>219</v>
       </c>
       <c r="B288" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C288">
         <v>5.5</v>
@@ -6068,7 +6080,7 @@
         <v>219</v>
       </c>
       <c r="B289" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C289">
         <v>5.5</v>
@@ -6085,7 +6097,7 @@
         <v>219</v>
       </c>
       <c r="B290" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C290">
         <v>5.5</v>
@@ -6102,7 +6114,7 @@
         <v>210</v>
       </c>
       <c r="B291" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C291">
         <v>6.5</v>
@@ -6119,7 +6131,7 @@
         <v>210</v>
       </c>
       <c r="B292" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C292">
         <v>6.5</v>
@@ -6136,7 +6148,7 @@
         <v>210</v>
       </c>
       <c r="B293" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C293">
         <v>6.5</v>
@@ -6153,7 +6165,7 @@
         <v>210</v>
       </c>
       <c r="B294" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C294">
         <v>6.5</v>
@@ -6170,7 +6182,7 @@
         <v>210</v>
       </c>
       <c r="B295" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C295">
         <v>6.5</v>
@@ -6187,7 +6199,7 @@
         <v>210</v>
       </c>
       <c r="B296" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C296">
         <v>6.5</v>
@@ -6204,7 +6216,7 @@
         <v>210</v>
       </c>
       <c r="B297" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C297">
         <v>6.5</v>
@@ -6221,7 +6233,7 @@
         <v>210</v>
       </c>
       <c r="B298" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C298">
         <v>6.5</v>
@@ -6238,7 +6250,7 @@
         <v>219</v>
       </c>
       <c r="B299" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C299">
         <v>6.5</v>
@@ -6255,7 +6267,7 @@
         <v>219</v>
       </c>
       <c r="B300" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C300">
         <v>6.5</v>
@@ -6272,7 +6284,7 @@
         <v>219</v>
       </c>
       <c r="B301" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C301">
         <v>6.5</v>
@@ -6289,7 +6301,7 @@
         <v>219</v>
       </c>
       <c r="B302" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="C302">
         <v>6.5</v>
@@ -6306,7 +6318,7 @@
         <v>219</v>
       </c>
       <c r="B303" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C303">
         <v>6.5</v>
@@ -6323,7 +6335,7 @@
         <v>219</v>
       </c>
       <c r="B304" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C304">
         <v>6.5</v>
@@ -6340,7 +6352,7 @@
         <v>219</v>
       </c>
       <c r="B305" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C305">
         <v>6.5</v>
@@ -6357,7 +6369,7 @@
         <v>219</v>
       </c>
       <c r="B306" t="s">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="C306">
         <v>6.5</v>
